--- a/tests/fixtures/sample.xlsx
+++ b/tests/fixtures/sample.xlsx
@@ -437,7 +437,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RNA-260527KAM-1</t>
+          <t>RNA-190902KAM-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -447,14 +447,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TIS-250218KAM-1</t>
+          <t>TIS-190905KAM-1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RNA-260527KAM-2</t>
+          <t>RNA-190902KAM-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TIS-250218KAM-1</t>
+          <t>TIS-190905KAM-1</t>
         </is>
       </c>
     </row>
